--- a/results/event_model_table.xlsx
+++ b/results/event_model_table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zoerand/Github Repos/Publications/UASalishSea/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{73666B0F-B53F-754F-99EC-C4DD3BB20E63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D21B8C2-C065-A040-989F-E54F80832E90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11200" yWindow="3060" windowWidth="26740" windowHeight="15500" xr2:uid="{4E73744A-CDFD-994A-BAD2-E491A0FE9F80}"/>
+    <workbookView xWindow="4100" yWindow="600" windowWidth="18840" windowHeight="15260" xr2:uid="{4E73744A-CDFD-994A-BAD2-E491A0FE9F80}"/>
   </bookViews>
   <sheets>
     <sheet name="event_model_ests" sheetId="1" r:id="rId1"/>
@@ -25,30 +25,6 @@
     <t>Estimate</t>
   </si>
   <si>
-    <t>siteWJF</t>
-  </si>
-  <si>
-    <t>siteAB</t>
-  </si>
-  <si>
-    <t>siteCJF</t>
-  </si>
-  <si>
-    <t>siteDB</t>
-  </si>
-  <si>
-    <t>siteHB</t>
-  </si>
-  <si>
-    <t>sitePA</t>
-  </si>
-  <si>
-    <t>siteSB</t>
-  </si>
-  <si>
-    <t>siteTTP</t>
-  </si>
-  <si>
     <t>speed</t>
   </si>
   <si>
@@ -56,6 +32,30 @@
   </si>
   <si>
     <t>Parameter</t>
+  </si>
+  <si>
+    <t>WJF</t>
+  </si>
+  <si>
+    <t>AB</t>
+  </si>
+  <si>
+    <t>CJF</t>
+  </si>
+  <si>
+    <t>DB</t>
+  </si>
+  <si>
+    <t>HB</t>
+  </si>
+  <si>
+    <t>PA</t>
+  </si>
+  <si>
+    <t>SB</t>
+  </si>
+  <si>
+    <t>TTP</t>
   </si>
 </sst>
 </file>
@@ -63,7 +63,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
@@ -542,11 +542,10 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -927,7 +926,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -941,142 +940,142 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B2" s="2">
-        <v>0.63477996600589104</v>
+        <v>0.63477986652656704</v>
       </c>
       <c r="C2" s="2">
-        <v>0.37430194262190503</v>
+        <v>0.37430194384276</v>
       </c>
       <c r="D2" s="2">
-        <v>0.89184931600377204</v>
+        <v>0.89184931574877402</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B3" s="2">
-        <v>2.6371409821827001E-2</v>
+        <v>0.66115126883408604</v>
       </c>
       <c r="C3" s="2">
-        <v>-0.65641280097176802</v>
+        <v>-4.4377933167572402E-2</v>
       </c>
       <c r="D3" s="2">
-        <v>0.56946339674401003</v>
+        <v>1.2373626185153701</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B4" s="2">
-        <v>-0.14180890578639499</v>
+        <v>0.49297103632682598</v>
       </c>
       <c r="C4" s="2">
-        <v>-0.28862764012064701</v>
+        <v>0.209905533609623</v>
       </c>
       <c r="D4" s="2">
-        <v>2.9561593245192299E-3</v>
+        <v>0.77144275752067004</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B5" s="2">
-        <v>7.6812518954174399E-3</v>
+        <v>0.64246110704411996</v>
       </c>
       <c r="C5" s="2">
-        <v>-0.19508134873324301</v>
+        <v>0.33017442816318598</v>
       </c>
       <c r="D5" s="2">
-        <v>0.201339207969644</v>
+        <v>0.94692808196426903</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B6" s="2">
-        <v>2.3139649322842602E-3</v>
+        <v>0.63709561146006899</v>
       </c>
       <c r="C6" s="2">
-        <v>-0.68365346899935397</v>
+        <v>-6.3431637371426097E-2</v>
       </c>
       <c r="D6" s="2">
-        <v>0.54962783423809702</v>
+        <v>1.20712122863931</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B7" s="2">
-        <v>-0.46136844538493399</v>
+        <v>0.17341153728157299</v>
       </c>
       <c r="C7" s="2">
-        <v>-0.66801044372240803</v>
+        <v>-0.130210493046863</v>
       </c>
       <c r="D7" s="2">
-        <v>-0.26385869308357401</v>
+        <v>0.47156973166279798</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B8" s="2">
-        <v>-0.39377513722243002</v>
-      </c>
-      <c r="C8" s="3">
-        <v>-1.0155954876492901</v>
+        <v>0.24100427027335999</v>
+      </c>
+      <c r="C8" s="2">
+        <v>-0.37868015717065401</v>
       </c>
       <c r="D8" s="2">
-        <v>0.118480669166244</v>
+        <v>0.74979565020121897</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B9" s="2">
-        <v>-0.55353589567031203</v>
-      </c>
-      <c r="C9" s="3">
-        <v>-1.6983758142830601</v>
+        <v>8.1244109566349296E-2</v>
+      </c>
+      <c r="C9" s="2">
+        <v>-1.07548041199904</v>
       </c>
       <c r="D9" s="2">
-        <v>0.250392408609178</v>
+        <v>0.90819017078971398</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B10" s="2">
-        <v>-7.4631712970220102E-2</v>
+        <v>-7.4631724673191305E-2</v>
       </c>
       <c r="C10" s="2">
-        <v>-8.9515730165909496E-2</v>
+        <v>-8.9515729693343302E-2</v>
       </c>
       <c r="D10" s="2">
-        <v>-5.9700255235417297E-2</v>
+        <v>-5.9700255229602497E-2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B11" s="2">
-        <v>0.21548915452276199</v>
+        <v>0.21548915408424699</v>
       </c>
       <c r="C11" s="2">
-        <v>0.19103651209143599</v>
+        <v>0.19103651212376299</v>
       </c>
       <c r="D11" s="2">
-        <v>0.23973081195558099</v>
+        <v>0.23973081225561599</v>
       </c>
     </row>
   </sheetData>
